--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="106" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="212" uniqueCount="31">
   <si>
     <t>Parameter</t>
   </si>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="212" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="265" uniqueCount="31">
   <si>
     <t>Parameter</t>
   </si>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="265" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="489" uniqueCount="34">
   <si>
     <t>Parameter</t>
   </si>
@@ -112,6 +112,15 @@
   </si>
   <si>
     <t>AvgWidth</t>
+  </si>
+  <si>
+    <t>Tmin</t>
+  </si>
+  <si>
+    <t>Tmax</t>
+  </si>
+  <si>
+    <t>T_{max}</t>
   </si>
 </sst>
 </file>
@@ -157,15 +166,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.5703125" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="16.5703125" customWidth="true"/>
+    <col min="6" max="6" width="15.85546875" customWidth="true"/>
     <col min="7" max="7" width="15.7109375" customWidth="true"/>
     <col min="8" max="8" width="14.7109375" customWidth="true"/>
   </cols>
@@ -201,25 +210,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2.4011272906495003</v>
+        <v>2.5022283310176143</v>
       </c>
       <c r="C2" s="0">
-        <v>0.25399530289342104</v>
+        <v>0.17429695035116216</v>
       </c>
       <c r="D2" s="0">
-        <v>10.5781690076379</v>
+        <v>6.9656692872739763</v>
       </c>
       <c r="E2" s="0">
-        <v>1.8597491177230006</v>
+        <v>-35629088882.477303</v>
       </c>
       <c r="F2" s="0">
-        <v>2.942505463576</v>
+        <v>35629088887.481758</v>
       </c>
       <c r="G2" s="0">
-        <v>1.5995804757467715</v>
+        <v>2.1405690855260229</v>
       </c>
       <c r="H2" s="0">
-        <v>2.7413999529417161</v>
+        <v>2.7739442537288235</v>
       </c>
     </row>
     <row r="3">
@@ -227,25 +236,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6.3797790688814402</v>
+        <v>6.2051212353762253</v>
       </c>
       <c r="C3" s="0">
-        <v>0.45652400670243237</v>
+        <v>0.34966562102214277</v>
       </c>
       <c r="D3" s="0">
-        <v>7.1557964903395037</v>
+        <v>5.635113445143543</v>
       </c>
       <c r="E3" s="0">
-        <v>5.4067211822584129</v>
+        <v>2.3032470099172211</v>
       </c>
       <c r="F3" s="0">
-        <v>7.3528369555044675</v>
+        <v>10.106995460835229</v>
       </c>
       <c r="G3" s="0">
-        <v>5.7614194585980663</v>
+        <v>5.7218654291766598</v>
       </c>
       <c r="H3" s="0">
-        <v>7.8193610686426673</v>
+        <v>7.0933453646415296</v>
       </c>
     </row>
     <row r="4">
@@ -253,25 +262,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>2.9212768015335824</v>
+        <v>4.5365827810155981</v>
       </c>
       <c r="C4" s="0">
-        <v>1.8073581626898421</v>
+        <v>0.98224134918517036</v>
       </c>
       <c r="D4" s="0">
-        <v>61.868774699509252</v>
+        <v>21.651568958370852</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.93101593299543062</v>
+        <v>-2.2020589912773163</v>
       </c>
       <c r="F4" s="0">
-        <v>6.7735695360625954</v>
+        <v>11.275224553308512</v>
       </c>
       <c r="G4" s="0">
-        <v>-0.62393805963429649</v>
+        <v>2.0683354995635015</v>
       </c>
       <c r="H4" s="0">
-        <v>5.3884634302910728</v>
+        <v>5.8745766601722709</v>
       </c>
     </row>
     <row r="5">
@@ -279,25 +288,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>0.0011351043537281111</v>
+        <v>0.0009813120988800782</v>
       </c>
       <c r="C5" s="0">
-        <v>0.00026282506035806057</v>
+        <v>8.4841204824390369e-05</v>
       </c>
       <c r="D5" s="0">
-        <v>23.154264142749863</v>
+        <v>8.6456902876480726</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00057490599826620257</v>
+        <v>0.00054267954320361242</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0016953027091900197</v>
+        <v>0.001419944654556544</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0008811761323918051</v>
+        <v>0.00083989535928024369</v>
       </c>
       <c r="H5" s="0">
-        <v>0.0021054594285657125</v>
+        <v>0.00113788210724989</v>
       </c>
     </row>
     <row r="6">
@@ -305,25 +314,51 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0.262067665103139</v>
+        <v>1.9635744033245664</v>
       </c>
       <c r="C6" s="0">
-        <v>0.21804380078990573</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>83.201336839511541</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.20268169500263161</v>
+        <v>-5.4112379704968726e+33</v>
       </c>
       <c r="F6" s="0">
-        <v>0.72681702520890967</v>
+        <v>5.4112379704968726e+33</v>
       </c>
       <c r="G6" s="0">
-        <v>0.065055771806588475</v>
+        <v>1.2388444249893504</v>
       </c>
       <c r="H6" s="0">
-        <v>2811.5120065093524</v>
+        <v>88771497.555350229</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="0">
+        <v>58.434841609505483</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0">
+        <v>-5.4112379704968738e+33</v>
+      </c>
+      <c r="F7" s="0">
+        <v>5.4112379704968738e+33</v>
+      </c>
+      <c r="G7" s="0">
+        <v>58.434841527741455</v>
+      </c>
+      <c r="H7" s="0">
+        <v>58.434841609505483</v>
       </c>
     </row>
   </sheetData>
@@ -352,7 +387,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="0">
-        <v>0.25241096223465936</v>
+        <v>0.25057450459097586</v>
       </c>
     </row>
     <row r="3">
@@ -360,7 +395,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="0">
-        <v>0.98740987697957872</v>
+        <v>0.9867652411268375</v>
       </c>
     </row>
     <row r="4">
@@ -368,7 +403,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="0">
-        <v>0.063711293856226647</v>
+        <v>0.062787582351012991</v>
       </c>
     </row>
     <row r="5">
@@ -376,7 +411,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="0">
-        <v>1.3148913532688742</v>
+        <v>1.2814569430618916</v>
       </c>
     </row>
     <row r="6">
@@ -393,15 +428,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
     <col min="2" max="2" width="13.42578125" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="13.42578125" customWidth="true"/>
-    <col min="5" max="5" width="13.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13.42578125" customWidth="true"/>
+    <col min="5" max="5" width="13.42578125" customWidth="true"/>
+    <col min="6" max="6" width="2.28515625" customWidth="true"/>
+    <col min="7" max="7" width="5.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,106 +459,107 @@
       <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.83405187984561358</v>
+        <v>-0.75590267435797898</v>
       </c>
       <c r="D2" s="0">
-        <v>0.80754290572151455</v>
+        <v>0.75573530519144205</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.28141874288228586</v>
-      </c>
-      <c r="F2" s="0">
-        <v>0.4588443003493099</v>
-      </c>
+        <v>0.33551652941862997</v>
+      </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.83405187984561358</v>
+        <v>-0.75590267435797887</v>
       </c>
       <c r="C3" s="0">
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.71147366651621658</v>
+        <v>-0.78760089574111558</v>
       </c>
       <c r="E3" s="0">
-        <v>0.049745436294107367</v>
-      </c>
-      <c r="F3" s="0">
-        <v>-0.31224224711391113</v>
-      </c>
+        <v>-0.63329368357471705</v>
+      </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.80754290572151455</v>
+        <v>0.75573530519144205</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.71147366651621658</v>
+        <v>-0.78760089574111558</v>
       </c>
       <c r="D4" s="0">
         <v>1.0000000000000002</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.60089359312370661</v>
-      </c>
-      <c r="F4" s="0">
-        <v>0.82597787427267944</v>
-      </c>
+        <v>0.82954170781979275</v>
+      </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.28141874288228586</v>
+        <v>0.33551652941862992</v>
       </c>
       <c r="C5" s="0">
-        <v>0.049745436294107367</v>
+        <v>-0.63329368357471716</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.60089359312370661</v>
+        <v>0.82954170781979275</v>
       </c>
       <c r="E5" s="0">
         <v>1</v>
       </c>
-      <c r="F5" s="0">
-        <v>-0.92997747654985097</v>
-      </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0">
-        <v>0.4588443003493099</v>
-      </c>
-      <c r="C6" s="0">
-        <v>-0.31224224711391113</v>
-      </c>
-      <c r="D6" s="0">
-        <v>0.82597787427267944</v>
-      </c>
-      <c r="E6" s="0">
-        <v>-0.92997747654985097</v>
-      </c>
-      <c r="F6" s="0">
-        <v>1.0000000000000002</v>
-      </c>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
     </row>
   </sheetData>
 </worksheet>
@@ -536,7 +573,7 @@
     <col min="1" max="1" width="8.42578125" customWidth="true"/>
     <col min="2" max="2" width="15.42578125" customWidth="true"/>
     <col min="3" max="3" width="15.42578125" customWidth="true"/>
-    <col min="4" max="4" width="15.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,10 +598,10 @@
         <v>2.4828735836087539</v>
       </c>
       <c r="C2" s="0">
-        <v>2.4707199891647407</v>
+        <v>2.5276884131885327</v>
       </c>
       <c r="D2" s="0">
-        <v>0.012153594444013205</v>
+        <v>-0.044814829579778781</v>
       </c>
     </row>
     <row r="3">
@@ -575,10 +612,10 @@
         <v>2.5976951859255122</v>
       </c>
       <c r="C3" s="0">
-        <v>2.5145072843445577</v>
+        <v>2.545726740887921</v>
       </c>
       <c r="D3" s="0">
-        <v>0.08318790158095446</v>
+        <v>0.051968445037591238</v>
       </c>
     </row>
     <row r="4">
@@ -589,10 +626,10 @@
         <v>2.5211380837040362</v>
       </c>
       <c r="C4" s="0">
-        <v>2.6128510557881133</v>
+        <v>2.5891734312280672</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.091712972084077027</v>
+        <v>-0.068035347524030954</v>
       </c>
     </row>
     <row r="5">
@@ -603,10 +640,10 @@
         <v>3.0733517023869008</v>
       </c>
       <c r="C5" s="0">
-        <v>3.1199753615810755</v>
+        <v>2.9496691899242786</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.04662365919417466</v>
+        <v>0.12368251246262219</v>
       </c>
     </row>
     <row r="6">
@@ -617,10 +654,10 @@
         <v>3.8808135922807914</v>
       </c>
       <c r="C6" s="0">
-        <v>3.8842414134559125</v>
+        <v>3.9100276933169846</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.0034278211751210819</v>
+        <v>-0.029214101036193263</v>
       </c>
     </row>
     <row r="7">
@@ -631,10 +668,10 @@
         <v>3.8987251815894934</v>
       </c>
       <c r="C7" s="0">
-        <v>3.8842414134559125</v>
+        <v>3.9100276933169846</v>
       </c>
       <c r="D7" s="0">
-        <v>0.014483768133580988</v>
+        <v>-0.011302511727491193</v>
       </c>
     </row>
     <row r="8">
@@ -645,10 +682,10 @@
         <v>4.9588504516796785</v>
       </c>
       <c r="C8" s="0">
-        <v>4.8887435268410187</v>
+        <v>4.9741102109361943</v>
       </c>
       <c r="D8" s="0">
-        <v>0.070106924838659879</v>
+        <v>-0.015259759256515792</v>
       </c>
     </row>
     <row r="9">
@@ -659,10 +696,10 @@
         <v>4.8619404386716223</v>
       </c>
       <c r="C9" s="0">
-        <v>4.8887435268410187</v>
+        <v>4.9741102109361943</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.026803088169396361</v>
+        <v>-0.11216977226457203</v>
       </c>
     </row>
     <row r="10">
@@ -673,10 +710,10 @@
         <v>5.3130231103232379</v>
       </c>
       <c r="C10" s="0">
-        <v>5.5484816669495958</v>
+        <v>5.5560095466842121</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.23545855662635784</v>
+        <v>-0.24298643636097417</v>
       </c>
     </row>
     <row r="11">
@@ -687,10 +724,10 @@
         <v>5.4817291969600159</v>
       </c>
       <c r="C11" s="0">
-        <v>5.5484816669495958</v>
+        <v>5.5560095466842121</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.066752469989579843</v>
+        <v>-0.074280349724196171</v>
       </c>
     </row>
     <row r="12">
@@ -701,10 +738,10 @@
         <v>5.4857214264815797</v>
       </c>
       <c r="C12" s="0">
-        <v>5.7526563053838951</v>
+        <v>5.7328312430278139</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.26693487890231538</v>
+        <v>-0.24710981654623421</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +752,10 @@
         <v>5.510545010206612</v>
       </c>
       <c r="C13" s="0">
-        <v>5.7526563053838951</v>
+        <v>5.7328312430278139</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.24211129517728303</v>
+        <v>-0.22228623282120186</v>
       </c>
     </row>
     <row r="14">
@@ -729,10 +766,10 @@
         <v>6.2294258479206954</v>
       </c>
       <c r="C14" s="0">
-        <v>5.7820690295333588</v>
+        <v>5.7595117380241385</v>
       </c>
       <c r="D14" s="0">
-        <v>0.44735681838733665</v>
+        <v>0.46991410989655691</v>
       </c>
     </row>
     <row r="15">
@@ -743,10 +780,10 @@
         <v>6.2435341018320623</v>
       </c>
       <c r="C15" s="0">
-        <v>5.7820690295333588</v>
+        <v>5.7595117380241385</v>
       </c>
       <c r="D15" s="0">
-        <v>0.46146507229870348</v>
+        <v>0.48402236380792374</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +794,10 @@
         <v>7.1679078100014797</v>
       </c>
       <c r="C16" s="0">
-        <v>7.2381557745292149</v>
+        <v>7.186576196526894</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.070247964527735185</v>
+        <v>-0.018668386525414249</v>
       </c>
     </row>
     <row r="17">
@@ -771,10 +808,10 @@
         <v>7.1726029312098598</v>
       </c>
       <c r="C17" s="0">
-        <v>7.2381557745292149</v>
+        <v>7.186576196526894</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.06555284331935507</v>
+        <v>-0.013973265317034134</v>
       </c>
     </row>
     <row r="18">
@@ -785,10 +822,10 @@
         <v>7.9405164849325676</v>
       </c>
       <c r="C18" s="0">
-        <v>8.2358795330772612</v>
+        <v>8.2558570027789315</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.29536304814469361</v>
+        <v>-0.31534051784636397</v>
       </c>
     </row>
     <row r="19">
@@ -799,10 +836,10 @@
         <v>7.9786369483844748</v>
       </c>
       <c r="C19" s="0">
-        <v>8.2358795330772612</v>
+        <v>8.2558570027789315</v>
       </c>
       <c r="D19" s="0">
-        <v>-0.25724258469278638</v>
+        <v>-0.27722005439445674</v>
       </c>
     </row>
     <row r="20">
@@ -813,10 +850,10 @@
         <v>8.5582284218033262</v>
       </c>
       <c r="C20" s="0">
-        <v>8.2885519084762169</v>
+        <v>8.2951047808829408</v>
       </c>
       <c r="D20" s="0">
-        <v>0.26967651332710929</v>
+        <v>0.26312364092038543</v>
       </c>
     </row>
     <row r="21">
@@ -827,10 +864,10 @@
         <v>8.5950550897593043</v>
       </c>
       <c r="C21" s="0">
-        <v>8.2885519084762169</v>
+        <v>8.2951047808829408</v>
       </c>
       <c r="D21" s="0">
-        <v>0.3065031812830874</v>
+        <v>0.29995030887636354</v>
       </c>
     </row>
   </sheetData>
@@ -839,15 +876,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
     <col min="3" max="3" width="12.7109375" customWidth="true"/>
     <col min="4" max="4" width="13.42578125" customWidth="true"/>
-    <col min="5" max="5" width="13.42578125" customWidth="true"/>
+    <col min="5" max="5" width="14.42578125" customWidth="true"/>
     <col min="6" max="6" width="15.42578125" customWidth="true"/>
+    <col min="7" max="7" width="14.7109375" customWidth="true"/>
+    <col min="8" max="8" width="15.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -869,25 +908,37 @@
       <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>2.6020599913278986</v>
+        <v>2.6020599913274545</v>
       </c>
       <c r="C2" s="0">
-        <v>0.64526262895991948</v>
+        <v>0.64533098884211881</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.28028777058874965</v>
+        <v>-0.28021934670618975</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.28028777058874965</v>
+        <v>-0.28021934670618975</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.0047050481288835036</v>
+        <v>-0.004692650009463506</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.17703102595501008</v>
+      </c>
+      <c r="H2" s="0">
+        <v>-0.010165451610255616</v>
       </c>
     </row>
     <row r="3">
@@ -895,19 +946,25 @@
         <v>0.5</v>
       </c>
       <c r="B3" s="0">
-        <v>2.6020599913278986</v>
+        <v>2.6020599913274545</v>
       </c>
       <c r="C3" s="0">
-        <v>0.65813525549796026</v>
+        <v>0.6581932284874803</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.29375384401841842</v>
+        <v>-0.29368412063002225</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.26798818152151682</v>
+        <v>-0.26793015273929299</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0040275356427699185</v>
+        <v>-0.0040165315220441755</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.17141095213490942</v>
+      </c>
+      <c r="H3" s="0">
+        <v>-0.008296710071853397</v>
       </c>
     </row>
     <row r="4">
@@ -915,19 +972,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>2.6020599913278986</v>
+        <v>2.6020599913274545</v>
       </c>
       <c r="C4" s="0">
-        <v>0.67589170773540985</v>
+        <v>0.67593500057716582</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.3146890990501916</v>
+        <v>-0.31461755996575747</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.24522883764088729</v>
+        <v>-0.2451855016563087</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.00042422611201686777</v>
+        <v>-0.00041951345197688283</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.16512953907232841</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0.002475483223296493</v>
       </c>
     </row>
     <row r="5">
@@ -935,19 +998,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="0">
-        <v>2.6020599913278986</v>
+        <v>2.6020599913274545</v>
       </c>
       <c r="C5" s="0">
-        <v>0.7093186430218168</v>
+        <v>0.70933337012712983</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.3698809790453339</v>
+        <v>-0.36980582679824181</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.16293231225095181</v>
+        <v>-0.16291756937247825</v>
       </c>
       <c r="F5" s="0">
-        <v>0.043555514706028468</v>
+        <v>0.043528379417345775</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.14880041346909678</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0.3465595152780665</v>
       </c>
     </row>
     <row r="6">
@@ -955,19 +1024,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C6" s="0">
-        <v>0.7245116160392584</v>
+        <v>0.7245128960398084</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.42385578165049509</v>
+        <v>-0.42377860366382691</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.051839152397370469</v>
+        <v>-0.051837870827853294</v>
       </c>
       <c r="F6" s="0">
-        <v>0.12668838307305919</v>
+        <v>0.12662719361378194</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.12619174871453254</v>
+      </c>
+      <c r="H6" s="0">
+        <v>1.3407054093743653</v>
       </c>
     </row>
     <row r="7">
@@ -975,19 +1050,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C7" s="0">
-        <v>0.7245116160392584</v>
+        <v>0.7245128960398084</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.42385578165049509</v>
+        <v>-0.42377860366382691</v>
       </c>
       <c r="E7" s="0">
-        <v>-0.051839152397370469</v>
+        <v>-0.051837870827853294</v>
       </c>
       <c r="F7" s="0">
-        <v>0.12668838307305919</v>
+        <v>0.12662719361378194</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.12619174871453254</v>
+      </c>
+      <c r="H7" s="0">
+        <v>1.3407054093743653</v>
       </c>
     </row>
     <row r="8">
@@ -995,19 +1076,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C8" s="0">
-        <v>0.72160072271287845</v>
+        <v>0.7216046658760078</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.48259561614472091</v>
+        <v>-0.48251786003961073</v>
       </c>
       <c r="E8" s="0">
-        <v>0.10548108316132954</v>
+        <v>0.10548503094343076</v>
       </c>
       <c r="F8" s="0">
-        <v>0.19958734816416524</v>
+        <v>0.19947809904952152</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.084065088722162784</v>
+      </c>
+      <c r="H8" s="0">
+        <v>1.9445205806620791</v>
       </c>
     </row>
     <row r="9">
@@ -1015,19 +1102,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C9" s="0">
-        <v>0.72160072271287845</v>
+        <v>0.7216046658760078</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.48259561614472091</v>
+        <v>-0.48251786003961073</v>
       </c>
       <c r="E9" s="0">
-        <v>0.10548108316132954</v>
+        <v>0.10548503094343076</v>
       </c>
       <c r="F9" s="0">
-        <v>0.19958734816416524</v>
+        <v>0.19947809904952152</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.084065088722162784</v>
+      </c>
+      <c r="H9" s="0">
+        <v>1.9445205806620791</v>
       </c>
     </row>
     <row r="10">
@@ -1035,19 +1128,25 @@
         <v>5</v>
       </c>
       <c r="B10" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C10" s="0">
-        <v>0.70913852508347475</v>
+        <v>0.70915362964463213</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.52055111145588029</v>
+        <v>-0.52047386008835517</v>
       </c>
       <c r="E10" s="0">
-        <v>0.22839786849360166</v>
+        <v>0.22841298978582003</v>
       </c>
       <c r="F10" s="0">
-        <v>0.22405415383452976</v>
+        <v>0.22392136594939771</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.035229916865553434</v>
+      </c>
+      <c r="H10" s="0">
+        <v>2.1277012487694869</v>
       </c>
     </row>
     <row r="11">
@@ -1055,19 +1154,25 @@
         <v>5</v>
       </c>
       <c r="B11" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C11" s="0">
-        <v>0.70913852508347475</v>
+        <v>0.70915362964463213</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.52055111145588029</v>
+        <v>-0.52047386008835517</v>
       </c>
       <c r="E11" s="0">
-        <v>0.22839786849360166</v>
+        <v>0.22841298978582003</v>
       </c>
       <c r="F11" s="0">
-        <v>0.22405415383452976</v>
+        <v>0.22392136594939771</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.035229916865553434</v>
+      </c>
+      <c r="H11" s="0">
+        <v>2.1277012487694869</v>
       </c>
     </row>
     <row r="12">
@@ -1075,19 +1180,25 @@
         <v>6</v>
       </c>
       <c r="B12" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C12" s="0">
-        <v>0.70335565969248393</v>
+        <v>0.70337590098068503</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.53273836235323557</v>
+        <v>-0.53266142018904006</v>
       </c>
       <c r="E12" s="0">
-        <v>0.27165083430258363</v>
+        <v>0.27167109776726761</v>
       </c>
       <c r="F12" s="0">
-        <v>0.22964091189958677</v>
+        <v>0.22950381936803765</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.0040371390279680952</v>
+      </c>
+      <c r="H12" s="0">
+        <v>2.1784987677775369</v>
       </c>
     </row>
     <row r="13">
@@ -1095,19 +1206,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C13" s="0">
-        <v>0.70335565969248393</v>
+        <v>0.70337590098068503</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.53273836235323557</v>
+        <v>-0.53266142018904006</v>
       </c>
       <c r="E13" s="0">
-        <v>0.27165083430258363</v>
+        <v>0.27167109776726761</v>
       </c>
       <c r="F13" s="0">
-        <v>0.22964091189958677</v>
+        <v>0.22950381936803765</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.0040371390279680952</v>
+      </c>
+      <c r="H13" s="0">
+        <v>2.1784987677775369</v>
       </c>
     </row>
     <row r="14">
@@ -1115,19 +1232,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C14" s="0">
-        <v>0.70238564711111451</v>
+        <v>0.70240674684862725</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.53460805417238078</v>
+        <v>-0.53453116633717102</v>
       </c>
       <c r="E14" s="0">
-        <v>0.27846714455215249</v>
+        <v>0.27848826736542876</v>
       </c>
       <c r="F14" s="0">
-        <v>0.23044942958794223</v>
+        <v>0.23031178277443942</v>
+      </c>
+      <c r="G14" s="0">
+        <v>-0.011010996031401987</v>
+      </c>
+      <c r="H14" s="0">
+        <v>2.1861407654730769</v>
       </c>
     </row>
     <row r="15">
@@ -1135,19 +1258,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C15" s="0">
-        <v>0.70238564711111451</v>
+        <v>0.70240674684862725</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.53460805417238078</v>
+        <v>-0.53453116633717102</v>
       </c>
       <c r="E15" s="0">
-        <v>0.27846714455215249</v>
+        <v>0.27848826736542876</v>
       </c>
       <c r="F15" s="0">
-        <v>0.23044942958794223</v>
+        <v>0.23031178277443942</v>
+      </c>
+      <c r="G15" s="0">
+        <v>-0.011010996031401987</v>
+      </c>
+      <c r="H15" s="0">
+        <v>2.1861407654730769</v>
       </c>
     </row>
     <row r="16">
@@ -1155,19 +1284,25 @@
         <v>12</v>
       </c>
       <c r="B16" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C16" s="0">
-        <v>0.61450280691044412</v>
+        <v>0.61459820942033616</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.63992286359670913</v>
+        <v>-0.63985182412729102</v>
       </c>
       <c r="E16" s="0">
-        <v>0.74087520297361209</v>
+        <v>0.74097069605416621</v>
       </c>
       <c r="F16" s="0">
-        <v>0.36050295459055798</v>
+        <v>0.36026675915534767</v>
+      </c>
+      <c r="G16" s="0">
+        <v>-0.21117962103867072</v>
+      </c>
+      <c r="H16" s="0">
+        <v>3.2515592909869717</v>
       </c>
     </row>
     <row r="17">
@@ -1175,19 +1310,25 @@
         <v>12</v>
       </c>
       <c r="B17" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913278986</v>
       </c>
       <c r="C17" s="0">
-        <v>0.61450280691044412</v>
+        <v>0.61459820942033616</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.63992286359670913</v>
+        <v>-0.63985182412729102</v>
       </c>
       <c r="E17" s="0">
-        <v>0.74087520297361209</v>
+        <v>0.74097069605416621</v>
       </c>
       <c r="F17" s="0">
-        <v>0.36050295459055798</v>
+        <v>0.36026675915534767</v>
+      </c>
+      <c r="G17" s="0">
+        <v>-0.21117962103867072</v>
+      </c>
+      <c r="H17" s="0">
+        <v>3.2515592909869717</v>
       </c>
     </row>
     <row r="18">
@@ -1195,19 +1336,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913270104</v>
       </c>
       <c r="C18" s="0">
-        <v>0.41854457733414563</v>
+        <v>0.41877501842169096</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.76411066658010895</v>
+        <v>-0.76405486905439801</v>
       </c>
       <c r="E18" s="0">
-        <v>1.552348556987937</v>
+        <v>1.5525791231985053</v>
       </c>
       <c r="F18" s="0">
-        <v>0.67119449273178589</v>
+        <v>0.67077361032907845</v>
+      </c>
+      <c r="G18" s="0">
+        <v>-0.50627962547000749</v>
+      </c>
+      <c r="H18" s="0">
+        <v>6.3657973887263353</v>
       </c>
     </row>
     <row r="19">
@@ -1215,19 +1362,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913270104</v>
       </c>
       <c r="C19" s="0">
-        <v>0.41854457733414563</v>
+        <v>0.41877501842169096</v>
       </c>
       <c r="D19" s="0">
-        <v>-0.76411066658010895</v>
+        <v>-0.76405486905439801</v>
       </c>
       <c r="E19" s="0">
-        <v>1.552348556987937</v>
+        <v>1.5525791231985053</v>
       </c>
       <c r="F19" s="0">
-        <v>0.67119449273178589</v>
+        <v>0.67077361032907845</v>
+      </c>
+      <c r="G19" s="0">
+        <v>-0.50627962547000749</v>
+      </c>
+      <c r="H19" s="0">
+        <v>6.3657973887263353</v>
       </c>
     </row>
     <row r="20">
@@ -1235,19 +1388,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913270104</v>
       </c>
       <c r="C20" s="0">
-        <v>0.3980033415285078</v>
+        <v>0.39824486129713677</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.77402490697764392</v>
+        <v>-0.77397083619157314</v>
       </c>
       <c r="E20" s="0">
-        <v>1.6353574998451137</v>
+        <v>1.6355991373888656</v>
       </c>
       <c r="F20" s="0">
-        <v>0.68032194247891187</v>
+        <v>0.67989241601917883</v>
+      </c>
+      <c r="G20" s="0">
+        <v>-0.57578987883477595</v>
+      </c>
+      <c r="H20" s="0">
+        <v>6.4487719102714891</v>
       </c>
     </row>
     <row r="21">
@@ -1255,19 +1414,25 @@
         <v>17</v>
       </c>
       <c r="B21" s="0">
-        <v>2.6020599913323395</v>
+        <v>2.6020599913270104</v>
       </c>
       <c r="C21" s="0">
-        <v>0.3980033415285078</v>
+        <v>0.39824486129713677</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.77402490697764392</v>
+        <v>-0.77397083619157314</v>
       </c>
       <c r="E21" s="0">
-        <v>1.6353574998451137</v>
+        <v>1.6355991373888656</v>
       </c>
       <c r="F21" s="0">
-        <v>0.68032194247891187</v>
+        <v>0.67989241601917883</v>
+      </c>
+      <c r="G21" s="0">
+        <v>-0.57578987883477595</v>
+      </c>
+      <c r="H21" s="0">
+        <v>6.4487719102714891</v>
       </c>
     </row>
   </sheetData>
@@ -1276,15 +1441,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
     <col min="4" max="4" width="13.42578125" customWidth="true"/>
-    <col min="5" max="5" width="13.42578125" customWidth="true"/>
-    <col min="6" max="6" width="15.42578125" customWidth="true"/>
+    <col min="5" max="5" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.5703125" customWidth="true"/>
+    <col min="7" max="7" width="15.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1306,25 +1472,31 @@
       <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>2.401127290649896</v>
+        <v>2.5022283310174309</v>
       </c>
       <c r="C2" s="0">
-        <v>0.22937811319234666</v>
+        <v>0.12412937619421527</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.15975685409230778</v>
+        <v>-0.098357624996658899</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.15975685409230775</v>
+        <v>-0.098357624996658899</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.0033694402956641052</v>
+        <v>0</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1332,19 +1504,22 @@
         <v>0.5</v>
       </c>
       <c r="B3" s="0">
-        <v>2.401127290649896</v>
+        <v>2.5022283310174309</v>
       </c>
       <c r="C3" s="0">
-        <v>0.29333160270539338</v>
+        <v>0.17343432237115763</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.23216061550979106</v>
+        <v>-0.15169481917443051</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.17993013695871693</v>
+        <v>-0.12962690301154822</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0026956677823264386</v>
+        <v>0</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1352,19 +1527,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>2.3965804995285107</v>
+        <v>2.5022283310174309</v>
       </c>
       <c r="C4" s="0">
-        <v>0.37861372576220015</v>
+        <v>0.26531144431229947</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.37335000989013872</v>
+        <v>-0.26592196784669398</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.16233424162681587</v>
+        <v>-0.17814686745776243</v>
       </c>
       <c r="F4" s="0">
-        <v>0.0093890291719134194</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1372,19 +1550,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="0">
-        <v>2.4102590039110079</v>
+        <v>2.5022283310174309</v>
       </c>
       <c r="C5" s="0">
-        <v>0.38094844044600501</v>
+        <v>0.42539566200527901</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.79438556323196963</v>
+        <v>-0.83853368941788631</v>
       </c>
       <c r="E5" s="0">
-        <v>0.3287681309727119</v>
+        <v>0.021933893689318751</v>
       </c>
       <c r="F5" s="0">
-        <v>0.26399117587949661</v>
+        <v>0</v>
+      </c>
+      <c r="G5" s="0">
+        <v>4.4408920985006262e-13</v>
       </c>
     </row>
     <row r="6">
@@ -1392,19 +1573,22 @@
         <v>3</v>
       </c>
       <c r="B6" s="0">
-        <v>2.4251218164872408</v>
+        <v>2.5022283310169868</v>
       </c>
       <c r="C6" s="0">
-        <v>0.15604774525002083</v>
+        <v>0.17977976880700908</v>
       </c>
       <c r="D6" s="0">
-        <v>-1.0874060845411646</v>
+        <v>-1.496979573108792</v>
       </c>
       <c r="E6" s="0">
-        <v>1.3030791729740088</v>
+        <v>1.2281502254056775</v>
       </c>
       <c r="F6" s="0">
-        <v>0.86919080004577143</v>
+        <v>1.3322676295501878e-12</v>
+      </c>
+      <c r="G6" s="0">
+        <v>3.9968028886505636e-12</v>
       </c>
     </row>
     <row r="7">
@@ -1412,19 +1596,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="0">
-        <v>2.4251218164872408</v>
+        <v>2.5022283310169868</v>
       </c>
       <c r="C7" s="0">
-        <v>0.15604774525002083</v>
+        <v>0.17977976880700908</v>
       </c>
       <c r="D7" s="0">
-        <v>-1.0874060845411646</v>
+        <v>-1.496979573108792</v>
       </c>
       <c r="E7" s="0">
-        <v>1.3030791729740088</v>
+        <v>1.2281502254056775</v>
       </c>
       <c r="F7" s="0">
-        <v>0.86919080004577143</v>
+        <v>1.3322676295501878e-12</v>
+      </c>
+      <c r="G7" s="0">
+        <v>3.9968028886505636e-12</v>
       </c>
     </row>
     <row r="8">
@@ -1432,19 +1619,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="0">
-        <v>2.4648569381469088</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C8" s="0">
-        <v>0.055659356830162203</v>
+        <v>0.030377185096241988</v>
       </c>
       <c r="D8" s="0">
-        <v>-1.1521316552354222</v>
+        <v>-1.6031674991348055</v>
       </c>
       <c r="E8" s="0">
-        <v>2.3681763056693228</v>
+        <v>2.441114823893642</v>
       </c>
       <c r="F8" s="0">
-        <v>1.3092302289052782</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G8" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="9">
@@ -1452,19 +1642,22 @@
         <v>4</v>
       </c>
       <c r="B9" s="0">
-        <v>2.4648569381469088</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C9" s="0">
-        <v>0.055659356830162203</v>
+        <v>0.030377185096241988</v>
       </c>
       <c r="D9" s="0">
-        <v>-1.1521316552354222</v>
+        <v>-1.6031674991348055</v>
       </c>
       <c r="E9" s="0">
-        <v>2.3681763056693228</v>
+        <v>2.441114823893642</v>
       </c>
       <c r="F9" s="0">
-        <v>1.3092302289052782</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G9" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1472,19 +1665,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="0">
-        <v>2.4645152112157116</v>
+        <v>2.5022283310169868</v>
       </c>
       <c r="C10" s="0">
-        <v>0.19976435823743086</v>
+        <v>0.16495232159385864</v>
       </c>
       <c r="D10" s="0">
-        <v>-1.0917885370442804</v>
+        <v>-1.5254996869487059</v>
       </c>
       <c r="E10" s="0">
-        <v>2.8840581833744494</v>
+        <v>2.8875340449339149</v>
       </c>
       <c r="F10" s="0">
-        <v>1.2982720980048155</v>
+        <v>1.7763568394002505e-12</v>
+      </c>
+      <c r="G10" s="0">
+        <v>4.4408920985006262e-12</v>
       </c>
     </row>
     <row r="11">
@@ -1492,19 +1688,22 @@
         <v>5</v>
       </c>
       <c r="B11" s="0">
-        <v>2.4645152112157116</v>
+        <v>2.5022283310169868</v>
       </c>
       <c r="C11" s="0">
-        <v>0.19976435823743086</v>
+        <v>0.16495232159385864</v>
       </c>
       <c r="D11" s="0">
-        <v>-1.0917885370442804</v>
+        <v>-1.5254996869487059</v>
       </c>
       <c r="E11" s="0">
-        <v>2.8840581833744494</v>
+        <v>2.8875340449339149</v>
       </c>
       <c r="F11" s="0">
-        <v>1.2982720980048155</v>
+        <v>1.7763568394002505e-12</v>
+      </c>
+      <c r="G11" s="0">
+        <v>4.4408920985006262e-12</v>
       </c>
     </row>
     <row r="12">
@@ -1512,19 +1711,22 @@
         <v>6</v>
       </c>
       <c r="B12" s="0">
-        <v>2.46307632206566</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C12" s="0">
-        <v>0.29223767556096902</v>
+        <v>0.24242774367166931</v>
       </c>
       <c r="D12" s="0">
-        <v>-1.0587427886488143</v>
+        <v>-1.4859275784013804</v>
       </c>
       <c r="E12" s="0">
-        <v>2.9971588861776866</v>
+        <v>2.9865377404671989</v>
       </c>
       <c r="F12" s="0">
-        <v>1.2614455969117697</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G12" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="13">
@@ -1532,19 +1734,22 @@
         <v>6</v>
       </c>
       <c r="B13" s="0">
-        <v>2.46307632206566</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C13" s="0">
-        <v>0.29223767556096902</v>
+        <v>0.24242774367166931</v>
       </c>
       <c r="D13" s="0">
-        <v>-1.0587427886488143</v>
+        <v>-1.4859275784013804</v>
       </c>
       <c r="E13" s="0">
-        <v>2.9971588861776866</v>
+        <v>2.9865377404671989</v>
       </c>
       <c r="F13" s="0">
-        <v>1.2614455969117697</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G13" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="14">
@@ -1552,19 +1757,22 @@
         <v>8</v>
       </c>
       <c r="B14" s="0">
-        <v>2.4648640320723558</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C14" s="0">
-        <v>0.30943661959881291</v>
+        <v>0.25588361619721667</v>
       </c>
       <c r="D14" s="0">
-        <v>-1.0520553442727731</v>
+        <v>-1.4792736109274784</v>
       </c>
       <c r="E14" s="0">
-        <v>3.0075771379056699</v>
+        <v>2.9997078806012212</v>
       </c>
       <c r="F14" s="0">
-        <v>1.2545784254758272</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G14" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="15">
@@ -1572,19 +1780,22 @@
         <v>8</v>
       </c>
       <c r="B15" s="0">
-        <v>2.4648640320723558</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C15" s="0">
-        <v>0.30943661959881291</v>
+        <v>0.25588361619721667</v>
       </c>
       <c r="D15" s="0">
-        <v>-1.0520553442727731</v>
+        <v>-1.4792736109274784</v>
       </c>
       <c r="E15" s="0">
-        <v>3.0075771379056699</v>
+        <v>2.9997078806012212</v>
       </c>
       <c r="F15" s="0">
-        <v>1.2545784254758272</v>
+        <v>2.6645352591003757e-12</v>
+      </c>
+      <c r="G15" s="0">
+        <v>5.3290705182007514e-12</v>
       </c>
     </row>
     <row r="16">
@@ -1592,19 +1803,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="0">
-        <v>2.4160191918820573</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C16" s="0">
-        <v>1.7867094348034127</v>
+        <v>1.7072862988971593</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.67326411110180107</v>
+        <v>-0.92825116149430897</v>
       </c>
       <c r="E16" s="0">
-        <v>3.0349157401321492</v>
+        <v>2.9721322114744098</v>
       </c>
       <c r="F16" s="0">
-        <v>1.0346141283612551</v>
+        <v>8.8817841970012523e-13</v>
+      </c>
+      <c r="G16" s="0">
+        <v>2.6645352591003757e-12</v>
       </c>
     </row>
     <row r="17">
@@ -1612,19 +1826,22 @@
         <v>12</v>
       </c>
       <c r="B17" s="0">
-        <v>2.4160191918820573</v>
+        <v>2.502228331017875</v>
       </c>
       <c r="C17" s="0">
-        <v>1.7867094348034127</v>
+        <v>1.7072862988971593</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.67326411110180107</v>
+        <v>-0.92825116149430897</v>
       </c>
       <c r="E17" s="0">
-        <v>3.0349157401321492</v>
+        <v>2.9721322114744098</v>
       </c>
       <c r="F17" s="0">
-        <v>1.0346141283612551</v>
+        <v>8.8817841970012523e-13</v>
+      </c>
+      <c r="G17" s="0">
+        <v>2.6645352591003757e-12</v>
       </c>
     </row>
     <row r="18">
@@ -1632,19 +1849,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="0">
-        <v>2.3999024679888237</v>
+        <v>2.5022283310160987</v>
       </c>
       <c r="C18" s="0">
-        <v>4.050153883312646</v>
+        <v>4.1929721856543978</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.26656445683670427</v>
+        <v>-0.30673117914759018</v>
       </c>
       <c r="E18" s="0">
-        <v>1.7852610184299065</v>
+        <v>1.5554954691126</v>
       </c>
       <c r="F18" s="0">
-        <v>0.62310470530846362</v>
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1652,19 +1872,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="0">
-        <v>2.3999024679888237</v>
+        <v>2.5022283310160987</v>
       </c>
       <c r="C19" s="0">
-        <v>4.050153883312646</v>
+        <v>4.1929721856543978</v>
       </c>
       <c r="D19" s="0">
-        <v>-0.26656445683670427</v>
+        <v>-0.30673117914759018</v>
       </c>
       <c r="E19" s="0">
-        <v>1.7852610184299065</v>
+        <v>1.5554954691126</v>
       </c>
       <c r="F19" s="0">
-        <v>0.62310470530846362</v>
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1672,19 +1895,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="0">
-        <v>2.3994130727977843</v>
+        <v>2.5022283310160987</v>
       </c>
       <c r="C20" s="0">
-        <v>4.2171875358398836</v>
+        <v>4.3253298874539326</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.24231007285990813</v>
+        <v>-0.28102683254260796</v>
       </c>
       <c r="E20" s="0">
-        <v>1.6714033020193142</v>
+        <v>1.4625294016923363</v>
       </c>
       <c r="F20" s="0">
-        <v>0.56625531110299221</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>1.7763568394002505e-12</v>
       </c>
     </row>
     <row r="21">
@@ -1692,19 +1918,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="0">
-        <v>2.3994130727977843</v>
+        <v>2.5022283310160987</v>
       </c>
       <c r="C21" s="0">
-        <v>4.2171875358398836</v>
+        <v>4.3253298874539326</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.24231007285990813</v>
+        <v>-0.28102683254260796</v>
       </c>
       <c r="E21" s="0">
-        <v>1.6714033020193142</v>
+        <v>1.4625294016923363</v>
       </c>
       <c r="F21" s="0">
-        <v>0.56625531110299221</v>
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>1.7763568394002505e-12</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1962,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="0">
-        <v>0.53067359191111618</v>
+        <v>0.44759373525871649</v>
       </c>
     </row>
     <row r="3">
@@ -1741,7 +1970,7 @@
         <v>27</v>
       </c>
       <c r="B3" s="0">
-        <v>0.4057657432934641</v>
+        <v>0.36022747266203525</v>
       </c>
     </row>
     <row r="4">
@@ -1749,7 +1978,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="0">
-        <v>1.2042171370317227</v>
+        <v>1.1549383750574016</v>
       </c>
     </row>
     <row r="5">
@@ -1757,7 +1986,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="0">
-        <v>1.0719562601251418</v>
+        <v>1.0472878538469919</v>
       </c>
     </row>
   </sheetData>
